--- a/inquiry_forms/022_product_availability_inquiry_contact_form--inquiry_forms.xlsx
+++ b/inquiry_forms/022_product_availability_inquiry_contact_form--inquiry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -974,7 +974,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>availability_status_label</t>
+          <t>availability_status_label_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>availability_status</t>
+          <t>availability_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Availability Status 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>availability_status_label</t>
+          <t>availability_status_label_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Availability Status Label</t>
+          <t>Availability Status Label 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>availability_status_options</t>
+          <t>availability_status_options_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Availability Status Options</t>
+          <t>Availability Status Options 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Product Description</t>
+          <t>Product Description Label</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>product_description</t>
+          <t>product_description_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Product Description</t>
+          <t>Product Description 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1229,29 +1229,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>availability_status_choices</t>
+          <t>availability_status_label_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>out_of_stock</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Out of Stock</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>out_of_stock</t>
+          <t>pre-order</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Out of Stock</t>
+          <t>Pre-Order</t>
         </is>
       </c>
     </row>
@@ -1297,29 +1297,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pre-order</t>
+          <t>discontinued</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pre-Order</t>
+          <t>Discontinued</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>availability_status_label_choices</t>
+          <t>contact_details_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>discontinued</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Discontinued</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>contact_details_choices</t>
+          <t>contact_number_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1399,29 +1399,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>contact_number_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1450,95 +1450,78 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>availability_status_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>availability_status_choices</t>
+          <t>availability_status_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>out_of_stock</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Out of Stock</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>availability_status_choices</t>
+          <t>availability_status_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>out_of_stock</t>
+          <t>pre-order</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Out of Stock</t>
+          <t>Pre-Order</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>availability_status_choices</t>
+          <t>availability_status_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pre-order</t>
+          <t>discontinued</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>Pre-Order</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>availability_status_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>discontinued</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
